--- a/data/trans_orig/P35_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2287</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2695</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>497</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2497</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -843,97 +843,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2334</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>507</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2921</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2541</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>3027</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>28642</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53249</t>
+          <t>52123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24759</t>
+          <t>25170</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>40455</t>
+          <t>41127</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57031</t>
+          <t>57850</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86117</t>
+          <t>86157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>258194</t>
+          <t>259320</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281613</t>
+          <t>282801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>247779</t>
+          <t>247341</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>264136</t>
+          <t>263460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>513940</t>
+          <t>513568</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>543715</t>
+          <t>542164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48141</t>
+          <t>50103</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>91858</t>
+          <t>92773</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63583</t>
+          <t>63587</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93747</t>
+          <t>92413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>119344</t>
+          <t>120605</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172335</t>
+          <t>174292</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1549</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5040</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107070</t>
+          <t>105499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154146</t>
+          <t>154339</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111894</t>
+          <t>111195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145851</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230456</t>
+          <t>228749</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>289330</t>
+          <t>286060</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285368</t>
+          <t>287158</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>345624</t>
+          <t>345025</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>283150</t>
+          <t>284281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>322731</t>
+          <t>324109</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>584253</t>
+          <t>585783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>656152</t>
+          <t>654092</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6232</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12313</t>
+          <t>11591</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68553</t>
+          <t>69213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96943</t>
+          <t>97644</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>81658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108771</t>
+          <t>108282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158487</t>
+          <t>160718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198551</t>
+          <t>199019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>214279</t>
+          <t>213061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>242141</t>
+          <t>243014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>232639</t>
+          <t>234178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>261417</t>
+          <t>262488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>454515</t>
+          <t>454971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>496822</t>
+          <t>495096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7462</t>
+          <t>7606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>20790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4538</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>48381</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77603</t>
+          <t>78538</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>49406</t>
+          <t>52185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107218</t>
+          <t>111003</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>109965</t>
+          <t>105402</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>177379</t>
+          <t>175836</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228957</t>
+          <t>228444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>259243</t>
+          <t>260314</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>356859</t>
+          <t>353252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>421272</t>
+          <t>417580</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,01%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>596128</t>
+          <t>596841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>668065</t>
+          <t>673615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>85,45%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10319</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26407</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23711</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23142</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44314</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17997</t>
+          <t>18958</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3789</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>12162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26801</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34606</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>33134</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48338</t>
+          <t>48401</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55406</t>
+          <t>56646</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77041</t>
+          <t>77480</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>114211</t>
+          <t>115055</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>134572</t>
+          <t>135932</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>135446</t>
+          <t>136294</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153745</t>
+          <t>154120</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>255807</t>
+          <t>254784</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>284918</t>
+          <t>282650</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -3575,97 +3575,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>680</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3509</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
         <is>
           <t>680</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>3553</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>3448</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -3688,97 +3688,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1391</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>801</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2857</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>69046</t>
+          <t>69497</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>95510</t>
+          <t>94720</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>65482</t>
+          <t>65849</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>85795</t>
+          <t>87802</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>140071</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>174352</t>
+          <t>174068</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>174126</t>
+          <t>174916</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>200590</t>
+          <t>200139</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>169376</t>
+          <t>168281</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>189775</t>
+          <t>189528</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>350956</t>
+          <t>351015</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>385085</t>
+          <t>384362</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>72,98%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15193</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2511</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14735</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,47 +4194,47 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>15957</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>7940</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>25622</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>1,74%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>15957</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>8879</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>25450</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3271</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14562</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21042</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10459</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>29892</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>111348</t>
+          <t>110355</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>152740</t>
+          <t>153886</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>97601</t>
+          <t>100984</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>268371</t>
+          <t>268606</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>206732</t>
+          <t>219226</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>389636</t>
+          <t>394851</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>454711</t>
+          <t>452899</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>498216</t>
+          <t>497208</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>556755</t>
+          <t>556399</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>743370</t>
+          <t>737013</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1041625</t>
+          <t>1040049</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1245268</t>
+          <t>1231147</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>66686</t>
+          <t>70693</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>217739</t>
+          <t>218354</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>123920</t>
+          <t>124216</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>161489</t>
+          <t>160450</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>179937</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>353831</t>
+          <t>359637</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>80558</t>
+          <t>81551</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>63156</t>
+          <t>62594</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>88810</t>
+          <t>90093</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>79741</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>158889</t>
+          <t>161505</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>86063</t>
+          <t>94182</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>290406</t>
+          <t>292500</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>230606</t>
+          <t>232555</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>275144</t>
+          <t>274429</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>294494</t>
+          <t>282251</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>554737</t>
+          <t>554177</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,72%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>352724</t>
+          <t>357064</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>751479</t>
+          <t>742073</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>223658</t>
+          <t>222787</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>269591</t>
+          <t>265010</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>591180</t>
+          <t>588687</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1086775</t>
+          <t>1101347</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>197361</t>
+          <t>190888</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>291370</t>
+          <t>290477</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>204602</t>
+          <t>206715</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>286856</t>
+          <t>287427</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>431360</t>
+          <t>436537</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>558136</t>
+          <t>561352</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>62702</t>
+          <t>63014</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>103078</t>
+          <t>103445</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>84247</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>125935</t>
+          <t>126208</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>155565</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>218111</t>
+          <t>217810</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>596184</t>
+          <t>587059</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>838612</t>
+          <t>837186</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>748005</t>
+          <t>716102</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>980549</t>
+          <t>983232</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1442636</t>
+          <t>1458872</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1778575</t>
+          <t>1787915</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>25,13%</t>
         </is>
       </c>
     </row>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2254994</t>
+          <t>2261121</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2597568</t>
+          <t>2616493</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2294154</t>
+          <t>2285001</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2612763</t>
+          <t>2650351</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4606494</t>
+          <t>4585586</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5082941</t>
+          <t>5067105</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>483</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>483</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2896</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>493</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>493</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>40439</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28642</t>
+          <t>30299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52123</t>
+          <t>52588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>33446</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25170</t>
+          <t>25880</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>41552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>70613</t>
+          <t>73885</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57850</t>
+          <t>61462</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86157</t>
+          <t>88571</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>272959</t>
+          <t>278406</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>259320</t>
+          <t>266257</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>282801</t>
+          <t>288546</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>256501</t>
+          <t>281639</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>247341</t>
+          <t>273818</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>263460</t>
+          <t>289532</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>529459</t>
+          <t>560045</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>513568</t>
+          <t>544666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>542164</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67437</t>
+          <t>68413</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>50103</t>
+          <t>50478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92773</t>
+          <t>90354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77453</t>
+          <t>88453</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63587</t>
+          <t>73393</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>92413</t>
+          <t>108631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>144890</t>
+          <t>156866</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>120605</t>
+          <t>130399</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>174292</t>
+          <t>185742</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1441</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>12441</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4891</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>9425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>10522</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17340</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129071</t>
+          <t>135370</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>105499</t>
+          <t>113910</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154339</t>
+          <t>162847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>128209</t>
+          <t>131616</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111195</t>
+          <t>115053</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145734</t>
+          <t>149461</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>257280</t>
+          <t>266986</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228749</t>
+          <t>239877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286060</t>
+          <t>297805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>317082</t>
+          <t>321233</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>287158</t>
+          <t>293448</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>345025</t>
+          <t>350572</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>303698</t>
+          <t>320812</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>284281</t>
+          <t>300120</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>324109</t>
+          <t>341762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>620780</t>
+          <t>642045</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>585783</t>
+          <t>608522</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>654092</t>
+          <t>677135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>514238</t>
+          <t>545772</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>514238</t>
+          <t>545772</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>514238</t>
+          <t>545772</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1032628</t>
+          <t>1076419</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1032628</t>
+          <t>1076419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1032628</t>
+          <t>1076419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,22 +1933,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -1976,22 +1976,22 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5203</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>14311</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2089,22 +2089,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>83277</t>
+          <t>85004</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69213</t>
+          <t>69210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97644</t>
+          <t>99060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>94821</t>
+          <t>98011</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>81658</t>
+          <t>84473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108282</t>
+          <t>111347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>178098</t>
+          <t>183015</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160718</t>
+          <t>163548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>199019</t>
+          <t>203531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>228479</t>
+          <t>226670</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213061</t>
+          <t>211595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243014</t>
+          <t>241656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>247493</t>
+          <t>251689</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234178</t>
+          <t>237159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>262488</t>
+          <t>264938</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>475973</t>
+          <t>478359</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>454971</t>
+          <t>458488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>495096</t>
+          <t>498736</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,48%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>348723</t>
+          <t>355972</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>664774</t>
+          <t>671965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>762</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7606</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7352</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20790</t>
+          <t>19157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>24431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>882</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>62061</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48381</t>
+          <t>61127</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>78538</t>
+          <t>99579</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>83999</t>
+          <t>94918</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52185</t>
+          <t>79456</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>111003</t>
+          <t>114572</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>146059</t>
+          <t>172585</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>105402</t>
+          <t>148577</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>175836</t>
+          <t>199985</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>245542</t>
+          <t>290140</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228444</t>
+          <t>267573</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>260314</t>
+          <t>307440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>383161</t>
+          <t>317960</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>353252</t>
+          <t>299027</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>417580</t>
+          <t>334263</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>628703</t>
+          <t>608100</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>596841</t>
+          <t>579976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>673615</t>
+          <t>630868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9124</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>28803</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>13247</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23282</t>
+          <t>31395</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>38724</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>28107</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44226</t>
+          <t>52923</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7373</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>19926</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12162</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>28655</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>21372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34527</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>41401</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33134</t>
+          <t>34033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48401</t>
+          <t>49435</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>65938</t>
+          <t>69931</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>56646</t>
+          <t>58587</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>77480</t>
+          <t>81179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>125517</t>
+          <t>145317</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>132848</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>135932</t>
+          <t>154614</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>144735</t>
+          <t>157744</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>136294</t>
+          <t>146693</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154120</t>
+          <t>167617</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>270252</t>
+          <t>303061</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>254784</t>
+          <t>287472</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282650</t>
+          <t>319111</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>207467</t>
+          <t>225978</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>207467</t>
+          <t>225978</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207467</t>
+          <t>225978</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>386209</t>
+          <t>431642</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>386209</t>
+          <t>431642</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>386209</t>
+          <t>431642</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>669</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3789</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>669</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>829</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2898</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>829</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3763,12 +3763,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>81566</t>
+          <t>79949</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>67679</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>94720</t>
+          <t>92045</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>75767</t>
+          <t>78473</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>65849</t>
+          <t>68151</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>87802</t>
+          <t>90395</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>157334</t>
+          <t>158422</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>140411</t>
+          <t>142736</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>174068</t>
+          <t>174799</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>188070</t>
+          <t>190758</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>174916</t>
+          <t>178662</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>200139</t>
+          <t>203028</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>179808</t>
+          <t>183779</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>168281</t>
+          <t>171894</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>189528</t>
+          <t>194179</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>367878</t>
+          <t>374537</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>351015</t>
+          <t>358436</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>384362</t>
+          <t>391199</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,2%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,102 +4139,102 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>23621</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>8948</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>4286</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>17203</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>21361</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>13420</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>35532</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>7026</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>2355</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>14547</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>15957</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>7940</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>25622</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20641</t>
+          <t>22428</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>18429</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>131022</t>
+          <t>153644</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>110355</t>
+          <t>132034</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>153886</t>
+          <t>180459</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>197112</t>
+          <t>236860</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>100984</t>
+          <t>212207</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>268606</t>
+          <t>261245</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>328134</t>
+          <t>390504</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>219226</t>
+          <t>360331</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>394851</t>
+          <t>423382</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>476894</t>
+          <t>545545</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>452899</t>
+          <t>518812</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>497208</t>
+          <t>567868</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>633298</t>
+          <t>512435</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>556399</t>
+          <t>487469</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>737013</t>
+          <t>535882</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1110192</t>
+          <t>1057980</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1040049</t>
+          <t>1021955</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1231147</t>
+          <t>1090305</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>73,13%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>848433</t>
+          <t>771193</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>848433</t>
+          <t>771193</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>848433</t>
+          <t>771193</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1472712</t>
+          <t>1490880</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1472712</t>
+          <t>1490880</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1472712</t>
+          <t>1490880</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>153832</t>
+          <t>180709</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>70693</t>
+          <t>156096</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>218354</t>
+          <t>207002</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>142680</t>
+          <t>168135</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>124216</t>
+          <t>147127</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>160450</t>
+          <t>189238</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>296512</t>
+          <t>348844</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>179937</t>
+          <t>317476</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>359637</t>
+          <t>382213</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>54565</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>52006</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>81551</t>
+          <t>83564</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>75116</t>
+          <t>86998</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>62594</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>90093</t>
+          <t>102656</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>129681</t>
+          <t>153833</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>79593</t>
+          <t>131289</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>161505</t>
+          <t>177108</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>206711</t>
+          <t>230406</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>94182</t>
+          <t>204291</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>292500</t>
+          <t>257615</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>253262</t>
+          <t>283349</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>232555</t>
+          <t>260263</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>274429</t>
+          <t>309096</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>459973</t>
+          <t>513754</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>282251</t>
+          <t>478332</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>554177</t>
+          <t>549767</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,77%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>513612</t>
+          <t>320122</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>357064</t>
+          <t>291213</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>742073</t>
+          <t>350789</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>243791</t>
+          <t>291514</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>222787</t>
+          <t>266982</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>265010</t>
+          <t>322145</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>757403</t>
+          <t>611637</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>588687</t>
+          <t>573879</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>1101347</t>
+          <t>653978</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>714849</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>714849</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>714849</t>
+          <t>829996</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1643570</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>1643570</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>1643570</t>
+          <t>1628068</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5277,32 +5277,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>250784</t>
+          <t>285161</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>190888</t>
+          <t>250295</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>290477</t>
+          <t>324539</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5312,32 +5312,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>252802</t>
+          <t>294975</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>206715</t>
+          <t>261820</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>287427</t>
+          <t>326249</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5347,32 +5347,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>503586</t>
+          <t>580135</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>436537</t>
+          <t>535725</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>561352</t>
+          <t>636233</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -5390,32 +5390,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>82969</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>63014</t>
+          <t>81195</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>103445</t>
+          <t>121037</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5425,32 +5425,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>105312</t>
+          <t>120063</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>82936</t>
+          <t>101698</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>126208</t>
+          <t>140616</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5460,32 +5460,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>188281</t>
+          <t>218463</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>156361</t>
+          <t>191229</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>217810</t>
+          <t>245245</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5503,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>757910</t>
+          <t>831009</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>587059</t>
+          <t>781410</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>837186</t>
+          <t>883940</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5538,32 +5538,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>905520</t>
+          <t>998074</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>716102</t>
+          <t>955359</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>983232</t>
+          <t>1046008</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5573,32 +5573,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>1663430</t>
+          <t>1829083</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1458872</t>
+          <t>1760189</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1787915</t>
+          <t>1898049</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -5616,32 +5616,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>2368154</t>
+          <t>2318192</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2261121</t>
+          <t>2253048</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2616493</t>
+          <t>2378110</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5651,32 +5651,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2392485</t>
+          <t>2317572</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2285001</t>
+          <t>2262407</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>2650351</t>
+          <t>2366738</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,32 +5686,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>4760640</t>
+          <t>4635764</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>4585586</t>
+          <t>4546423</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5067105</t>
+          <t>4708190</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3656119</t>
+          <t>3730683</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5799,17 +5799,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7115936</t>
+          <t>7263445</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
